--- a/test-documents/quarterly-financial-report.xlsx
+++ b/test-documents/quarterly-financial-report.xlsx
@@ -1,59 +1,91 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" r:id="rId1"/>
-    <sheet name="Regional Breakdown" sheetId="2" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profit &amp; Loss" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Invoice Tracker" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="8">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00315CF6"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="00111827"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00315CF6"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00059669"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00D97706"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00315CF6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F1F5F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -61,18 +93,126 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="12">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -151,7 +291,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -186,7 +325,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -221,16 +359,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -352,193 +494,1083 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Quarter</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Revenue (INR)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Expenses (INR)</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Net Profit (INR)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Q1 FY2026-27</v>
-      </c>
-      <c r="B2">
-        <v>1250000</v>
-      </c>
-      <c r="C2">
-        <v>980000</v>
-      </c>
-      <c r="D2">
-        <v>270000</v>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>NextUpgrad Web Solutions — Profit &amp; Loss Statement (FY 2025-26)</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>Q2 FY2026-27</v>
-      </c>
-      <c r="B3">
-        <v>1420000</v>
-      </c>
-      <c r="C3">
-        <v>1050000</v>
-      </c>
-      <c r="D3">
-        <v>370000</v>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Line Item</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Q1 FY26 (₹)</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Q2 FY26 (₹)</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Q3 FY26 (₹)</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Q4 FY26 (₹)</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>FY26 Total (₹)</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>Q3 FY2026-27</v>
-      </c>
-      <c r="B4">
-        <v>1380000</v>
-      </c>
-      <c r="C4">
-        <v>1010000</v>
-      </c>
-      <c r="D4">
-        <v>370000</v>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Revenue from Operations</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>3612300</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>4018750</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>4420600</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>4820450</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>16872100</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v>Q4 FY2026-27</v>
-      </c>
-      <c r="B5">
-        <v>1600000</v>
-      </c>
-      <c r="C5">
-        <v>1150000</v>
-      </c>
-      <c r="D5">
-        <v>450000</v>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Other Income</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>45200</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>52100</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>61800</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>74500</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>233600</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Total Income</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>3657500</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>4070850</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>4482400</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>4894950</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>17105700</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr"/>
+      <c r="B7" s="4" t="inlineStr"/>
+      <c r="C7" s="4" t="inlineStr"/>
+      <c r="D7" s="4" t="inlineStr"/>
+      <c r="E7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Cost of Services</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>2014200</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>2219100</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>2431500</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>2648200</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>9313000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Employee Benefit Expense</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>832500</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>911300</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>1005200</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>1098600</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>3847600</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Technology &amp; Infrastructure</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>180400</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>195300</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>211700</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>234500</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>821900</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Sales &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>92300</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>104800</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>115900</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>128700</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>441700</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>General &amp; Administrative</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>74100</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>81200</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>89400</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>97800</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>342500</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>38200</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>38200</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>38200</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>38200</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>152800</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Total Expenses</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>3131700</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>3549900</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>3891900</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>4246000</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>14919500</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr"/>
+      <c r="B15" s="4" t="inlineStr"/>
+      <c r="C15" s="4" t="inlineStr"/>
+      <c r="D15" s="4" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>525800</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>520950</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>590500</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>648950</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>2286200</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>EBIT</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>487600</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>482750</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>552300</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>610750</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>2133400</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>PBT</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>471200</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>468400</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>536100</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>594200</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>2069900</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Tax Expense</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>117800</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>117100</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>134025</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>148550</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>517475</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>PAT (Net Profit)</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>353400</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>351300</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>402075</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>445650</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>1552425</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D5"/>
-  </ignoredErrors>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Region</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Q4 Revenue (INR)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>YoY Growth</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>North</v>
-      </c>
-      <c r="B2">
-        <v>480000</v>
-      </c>
-      <c r="C2" t="str">
-        <v>12%</v>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>NextUpgrad Web Solutions — Balance Sheet as at 31 March 2026</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>South</v>
-      </c>
-      <c r="B3">
-        <v>620000</v>
-      </c>
-      <c r="C3" t="str">
-        <v>18%</v>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Particulars</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>FY26 (₹)</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>FY25 (₹)</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>East</v>
-      </c>
-      <c r="B4">
-        <v>260000</v>
-      </c>
-      <c r="C4" t="str">
-        <v>5%</v>
-      </c>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>EQUITY &amp; LIABILITIES</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="inlineStr"/>
+      <c r="D4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v>West</v>
-      </c>
-      <c r="B5">
-        <v>240000</v>
-      </c>
-      <c r="C5" t="str">
-        <v>9%</v>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Share Capital</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>12,00,00,000</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>12,00,00,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Other Equity / Reserves</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>48,32,15,425</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>32,79,75,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Total Equity</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>60,32,15,425</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>44,79,75,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Long-term Borrowings</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>5,50,00,000</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>8,25,00,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Deferred Tax Liabilities</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>45,32,000</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>52,18,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>8,14,27,800</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>7,31,45,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL LIABILITIES</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr"/>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>74,41,75,225</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>60,88,38,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr"/>
+      <c r="B12" s="3" t="inlineStr"/>
+      <c r="C12" s="3" t="inlineStr"/>
+      <c r="D12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>ASSETS</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="inlineStr"/>
+      <c r="D13" s="6" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Property, Plant &amp; Equipment</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>6,32,14,000</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>7,11,22,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Intangibles (Software/IP)</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>3,45,80,000</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>2,98,30,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Investments</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>14,00,00,000</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>10,00,00,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Trade Receivables</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>22,18,45,225</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>18,32,18,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Cash &amp; Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>18,91,36,000</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>13,62,67,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Other Current Assets</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>9,54,00,000</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>8,84,00,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL ASSETS</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr"/>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>74,41,75,225</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>60,88,38,200</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C5"/>
-  </ignoredErrors>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Accounts Receivable — Invoice Tracker (Aug 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Invoice No</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Due Date</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Amount (₹)</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Days Overdue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>NGWS-SVC-2026-028</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Reliance Future Tech Ltd.</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>05-Jul-26</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>04-Aug-26</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>14,85,000</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>PAID</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>NGWS-SVC-2026-029</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>ICICI Prudential AMC</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>10-Jul-26</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>09-Aug-26</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>8,42,000</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>PAID</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>NGWS-SVC-2026-030</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Infosys BPM Ltd.</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>18-Jul-26</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>17-Aug-26</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>22,10,000</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>NGWS-SVC-2026-031</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Reliance Future Tech Ltd.</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>10-Aug-26</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>24-Aug-26</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>16,48,080</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>ISSUED</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>INV-2026-08-0147</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>NextUpgrad (Internal Test)</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>10-Aug-26</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>09-Sep-26</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>3,50,600</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>ISSUED</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>NGWS-SVC-2026-027</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>20-Jun-26</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>20-Jul-26</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>31,00,000</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="inlineStr">
+        <is>
+          <t>OVERDUE</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>